--- a/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ (Бер., Мел.)/дв 21,07,26 млрсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет ПОКОМ ЗПФ (Бер., Мел.)/дв 21,07,26 млрсч пок зпф.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ (Бер., Мел.)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ ЗПФ (Бер., Мел.)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5729636-90A0-4CC0-948F-C37DF8944BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E08796-5A0E-4310-83F5-A54EB850130E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AL$67</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="169">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -528,6 +536,9 @@
   <si>
     <t>Чебуреки сочные, ВЕС, куриные жарен. зам  ПОКОМ</t>
   </si>
+  <si>
+    <t>Пельмени С говядиной и свининой, ВЕС, ТМ Славница сфера пуговки  ПОКОМ</t>
+  </si>
 </sst>
 </file>
 
@@ -538,7 +549,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -579,6 +590,13 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2C2D2E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="7">
@@ -652,7 +670,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -675,6 +693,7 @@
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -9093,7 +9112,9 @@
       <c r="AW67" s="1"/>
     </row>
     <row r="68" spans="1:49" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
+      <c r="A68" s="22" t="s">
+        <v>168</v>
+      </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -31127,5 +31148,6 @@
   </sheetData>
   <autoFilter ref="A3:AL67" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>